--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484707_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484707_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.593400000000001</v>
+        <v>10.7195</v>
       </c>
       <c r="E2" t="n">
-        <v>8.762</v>
+        <v>10.012</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8313</v>
+        <v>0.7075</v>
       </c>
       <c r="G2" t="n">
         <v>3.4339</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2462</v>
+        <v>0.8799</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7903</v>
+        <v>0.4597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5441</v>
+        <v>0.4202</v>
       </c>
       <c r="V2" t="n">
         <v>4.7563</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7361</v>
+        <v>4.7687</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2482</v>
+        <v>3.479</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4879</v>
+        <v>1.2897</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2206</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2683</v>
+        <v>1.3009</v>
       </c>
       <c r="T3" t="n">
-        <v>1.408</v>
+        <v>0.6388</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8603</v>
+        <v>0.6621</v>
       </c>
       <c r="V3" t="n">
         <v>2.2224</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>I. DE LA IGLESIA SANTAMARIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3794</v>
+        <v>2.2648</v>
       </c>
       <c r="E4" t="n">
-        <v>1.284</v>
+        <v>3.3954</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0953</v>
+        <v>-1.1306</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0058</v>
+        <v>3.7516</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1728</v>
+        <v>0.2799</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1671</v>
+        <v>3.4717</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5314</v>
+        <v>4.1549</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1211</v>
+        <v>0.1701</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5897</v>
+        <v>3.9848</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5256</v>
+        <v>-0.4033</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0517</v>
+        <v>0.1098</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5774</v>
+        <v>-0.5131</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7559</v>
+        <v>0.6965</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8288</v>
+        <v>0.4291</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9271</v>
+        <v>0.2673</v>
       </c>
       <c r="V4" t="n">
-        <v>1.267</v>
+        <v>-1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>0.6439</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DE LA IGLESIA SANTAMARIA</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6058</v>
+        <v>1.9749</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5877</v>
+        <v>0.2263</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9819</v>
+        <v>1.7485</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7516</v>
+        <v>1.0058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2799</v>
+        <v>3.1728</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4717</v>
+        <v>-2.1671</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1549</v>
+        <v>1.5314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1701</v>
+        <v>3.1211</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9848</v>
+        <v>-1.5897</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4033</v>
+        <v>-0.5256</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1098</v>
+        <v>0.0517</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5131</v>
+        <v>-0.5774</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0374</v>
+        <v>1.3514</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6214</v>
+        <v>0.7711</v>
       </c>
       <c r="U5" t="n">
-        <v>0.416</v>
+        <v>0.5803</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.267</v>
+        <v>1.267</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6439</v>
+        <v>1.5889</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2502</v>
+        <v>1.4379</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2502</v>
+        <v>3.4851</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-2.0472</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2502</v>
+        <v>2.4667</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.7711</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2502</v>
+        <v>1.6956</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2502</v>
+        <v>2.1647</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.7895</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2502</v>
+        <v>1.3753</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.0184</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3204</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.6765</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.5483</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2397</v>
+        <v>1.2502</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4851</v>
+        <v>1.2502</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2454</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4667</v>
+        <v>1.2502</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7711</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6956</v>
+        <v>1.2502</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1647</v>
+        <v>1.2502</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7895</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3753</v>
+        <v>1.2502</v>
       </c>
       <c r="M7" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0184</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3204</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6765</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7465000000000001</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>A. RUIZ FRAGUEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9502</v>
+        <v>1.1618</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9502</v>
+        <v>-0.3501</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.5119</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9502</v>
+        <v>1.574</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3251</v>
+        <v>1.609</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-0.035</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9502</v>
+        <v>1.176</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3251</v>
+        <v>1.1146</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>0.0614</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4944</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.0964</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.4855</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0154</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PALAU LOPEZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,37 +1111,37 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2999</v>
+        <v>0.9502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3885</v>
+        <v>0.9502</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0885</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2999</v>
+        <v>0.9502</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2583</v>
+        <v>0.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3885</v>
+        <v>0.9502</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3468</v>
+        <v>0.3251</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0885</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0885</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUIZ FRAGUEIRO</t>
+          <t>A. PALAU LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1726</v>
+        <v>0.3961</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2155</v>
+        <v>0.4846</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3881</v>
+        <v>-0.0885</v>
       </c>
       <c r="G10" t="n">
-        <v>1.574</v>
+        <v>0.2999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.609</v>
+        <v>0.2583</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.035</v>
+        <v>0.0417</v>
       </c>
       <c r="J10" t="n">
-        <v>1.176</v>
+        <v>0.3885</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1146</v>
+        <v>0.3468</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0614</v>
+        <v>0.0417</v>
       </c>
       <c r="M10" t="n">
-        <v>0.398</v>
+        <v>-0.0885</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4944</v>
+        <v>-0.0885</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0964</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4747</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8808</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5939</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0919</v>
+        <v>-1.4706</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7637</v>
+        <v>-2.3406</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6718</v>
+        <v>0.87</v>
       </c>
       <c r="G11" t="n">
         <v>-0.325</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2777</v>
+        <v>-0.1011</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1524</v>
+        <v>0.5754</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8747</v>
+        <v>-0.6765</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3115</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.671</v>
+        <v>-3.4976</v>
       </c>
       <c r="E12" t="n">
         <v>-3.7929</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1219</v>
+        <v>0.2953</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7838</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3429</v>
+        <v>-0.1695</v>
       </c>
       <c r="T12" t="n">
         <v>0.2911</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.634</v>
+        <v>-0.4606</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6439</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5851</v>
+        <v>-4.0766</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3571</v>
+        <v>-2.9725</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.228</v>
+        <v>-1.1041</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1518</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1007</v>
+        <v>0.6092</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2557</v>
+        <v>0.6403</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.155</v>
+        <v>-0.0311</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1504,22 +1504,22 @@
         <v>15.8793</v>
       </c>
       <c r="E14" t="n">
-        <v>13.82670000000001</v>
+        <v>13.8267</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0525</v>
+        <v>2.052499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.251100000000001</v>
+        <v>6.251099999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4872</v>
+        <v>4.487200000000001</v>
       </c>
       <c r="I14" t="n">
         <v>1.763899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.605499999999996</v>
+        <v>7.605499999999999</v>
       </c>
       <c r="K14" t="n">
         <v>4.0761</v>
@@ -1549,10 +1549,10 @@
         <v>4.3062</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5628</v>
+        <v>4.562800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2566000000000007</v>
+        <v>-0.2566000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.4894</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2736</v>
+        <v>1.7214</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7513</v>
+        <v>5.1743</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.4777</v>
+        <v>-3.4529</v>
       </c>
       <c r="G15" t="n">
         <v>3.8803</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0346</v>
+        <v>-0.5175</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6026</v>
+        <v>0.0257</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5432</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4581</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1089</v>
+        <v>0.7272</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1094</v>
+        <v>2.6286</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0005</v>
+        <v>-1.9014</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2259</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1935</v>
+        <v>-0.1882</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6931</v>
+        <v>0.2123</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4996</v>
+        <v>-0.4005</v>
       </c>
       <c r="V16" t="n">
         <v>2.0417</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8548</v>
+        <v>0.6251</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0199</v>
+        <v>0.6251</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8348</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2475</v>
+        <v>0.6251</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1917</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4392</v>
+        <v>0.6251</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3994</v>
+        <v>0.6251</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1336</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7342</v>
+        <v>0.6251</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6469</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0581</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7983</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3356</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5373</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1911</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6251</v>
+        <v>0.377</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6251</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.9339</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6251</v>
+        <v>0.2475</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.1917</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6251</v>
+        <v>1.4392</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6251</v>
+        <v>-0.3994</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1.1336</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6251</v>
+        <v>0.7342</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.6469</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.0581</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.3205</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.7587</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.4382</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1911</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1911</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>J. ROMERA GALINDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5118</v>
+        <v>-0.6118</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8864</v>
+        <v>0.0217</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3747</v>
+        <v>-0.6335</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9283</v>
+        <v>-0.4836</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3869</v>
+        <v>-0.1951</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5415</v>
+        <v>-0.2885</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9638</v>
+        <v>0.0217</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8388</v>
+        <v>0.0217</v>
       </c>
       <c r="L20" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0354</v>
+        <v>-0.5053</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4519</v>
+        <v>-0.2167</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4164</v>
+        <v>-0.2885</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.228</v>
+        <v>-0.1282</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0384</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2665</v>
+        <v>-0.1282</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7519</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROMERA GALINDO</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6118</v>
+        <v>-0.7624</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0217</v>
+        <v>-0.7903</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6335</v>
+        <v>0.0278</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4836</v>
+        <v>0.9283</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1951</v>
+        <v>0.3869</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2885</v>
+        <v>0.5415</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0217</v>
+        <v>0.9638</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0217</v>
+        <v>0.8388</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5053</v>
+        <v>-0.0354</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2167</v>
+        <v>-0.4519</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2885</v>
+        <v>0.4164</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1282</v>
+        <v>-0.0226</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.0577</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1282</v>
+        <v>-0.0803</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7519</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.7727000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8289</v>
+        <v>-1.587</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1623</v>
+        <v>0.3546</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9911</v>
+        <v>-1.9416</v>
       </c>
       <c r="G23" t="n">
         <v>-1.403</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3137</v>
+        <v>-0.1214</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6797</v>
+        <v>-0.6301</v>
       </c>
       <c r="V23" t="n">
         <v>0.3843</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9587</v>
+        <v>-1.928</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0987</v>
+        <v>-2.291</v>
       </c>
       <c r="F24" t="n">
-        <v>0.14</v>
+        <v>0.363</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3439</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0559</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5294</v>
+        <v>0.3371</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4735</v>
+        <v>-0.2506</v>
       </c>
       <c r="V24" t="n">
         <v>0.0623</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1347</v>
+        <v>-1.9473</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3461</v>
+        <v>-0.4807</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7886</v>
+        <v>-1.4666</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4585</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8381</v>
+        <v>-0.6506</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0648</v>
+        <v>-0.1994</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7732</v>
+        <v>-0.4512</v>
       </c>
       <c r="V25" t="n">
         <v>0.0623</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9131</v>
+        <v>-3.7019</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9222</v>
+        <v>-2.5376</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9909</v>
+        <v>-1.1643</v>
       </c>
       <c r="G26" t="n">
         <v>0.1725</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6171</v>
+        <v>-1.4059</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6795</v>
+        <v>-0.2949</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9377</v>
+        <v>-1.1111</v>
       </c>
       <c r="V26" t="n">
         <v>-2.102</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.0463</v>
+        <v>-7.0551</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.891</v>
+        <v>-3.6025</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1553</v>
+        <v>-3.4526</v>
       </c>
       <c r="G27" t="n">
         <v>-2.8382</v>
@@ -2560,13 +2560,13 @@
         <v>0.733</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6552</v>
+        <v>-0.664</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8077</v>
+        <v>-0.5192</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1525</v>
+        <v>-0.1448</v>
       </c>
       <c r="V27" t="n">
         <v>-1.537</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.8793</v>
+        <v>-15.8792</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.052400000000001</v>
+        <v>-2.052500000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-13.8269</v>
+        <v>-13.827</v>
       </c>
       <c r="G28" t="n">
         <v>-6.2512</v>
@@ -2614,7 +2614,7 @@
         <v>1.3545</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4108999999999994</v>
+        <v>-0.4108999999999998</v>
       </c>
       <c r="L28" t="n">
         <v>1.7654</v>
@@ -2638,10 +2638,10 @@
         <v>9.162700000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.3063</v>
+        <v>-4.3061</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2565999999999998</v>
+        <v>0.2566000000000001</v>
       </c>
       <c r="U28" t="n">
         <v>-4.5628</v>
